--- a/output/pdf_financials_xlsx/NFG.xlsx
+++ b/output/pdf_financials_xlsx/NFG.xlsx
@@ -2470,19 +2470,19 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>30.474764</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>33.44721</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>34.755069</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>34.988421</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>42.820506</v>
       </c>
     </row>
     <row r="93">
@@ -4496,7 +4496,11 @@
           <t>Reserves 16</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -5575,7 +5579,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" s="5" t="n">
         <v>30.474764</v>
       </c>
@@ -6043,7 +6051,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NFG.xlsx
+++ b/output/pdf_financials_xlsx/NFG.xlsx
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.122714</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>1.220279</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>2.791248</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>2.869403</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>1.418145</v>
       </c>
     </row>
     <row r="13">
@@ -1023,19 +1023,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-50.640075</v>
+        <v>-50.762789</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-89.989659</v>
+        <v>-91.20993799999999</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-79.89076300000001</v>
+        <v>-82.682011</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-50.268354</v>
+        <v>-53.137757</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-47.57262</v>
+        <v>-48.990765</v>
       </c>
     </row>
     <row r="28">
@@ -1067,19 +1067,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-50.057145</v>
+        <v>-50.179859</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-89.109263</v>
+        <v>-90.329542</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-78.95055499999999</v>
+        <v>-81.741803</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-49.4547</v>
+        <v>-52.324103</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-46.744741</v>
+        <v>-48.162886</v>
       </c>
     </row>
     <row r="30">
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-804.976034846382</v>
+        <v>-829.3974502722847</v>
       </c>
     </row>
     <row r="31">
@@ -1178,13 +1178,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>100.484576</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>82.165273</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>53.884809</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>22.317548</v>
@@ -1222,13 +1222,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>100.484576</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>82.165273</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>53.884809</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>22.317548</v>
@@ -1486,13 +1486,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>136.520649</v>
+        <v>36.036073</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>94.33273</v>
+        <v>12.167457</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>62.300204</v>
+        <v>8.415395</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>5.223914</v>
@@ -3161,13 +3161,13 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.1005</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.121775</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.171076</v>
       </c>
       <c r="E124" s="3" t="n">
         <v>0</v>
@@ -3183,13 +3183,13 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.1005</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.121775</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.171076</v>
       </c>
       <c r="E125" s="3" t="n">
         <v>0</v>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
@@ -10190,7 +10190,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E167" s="5" t="n">
         <v>-0.1005</v>
       </c>
@@ -11229,7 +11233,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -12386,7 +12390,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -12427,7 +12431,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -13194,7 +13198,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -13647,7 +13651,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E252" s="5" t="n">
@@ -13690,7 +13694,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E253" s="5" t="n">

--- a/output/pdf_financials_xlsx/NFG.xlsx
+++ b/output/pdf_financials_xlsx/NFG.xlsx
@@ -2901,7 +2901,7 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.009084</v>
       </c>
       <c r="E112" s="3" t="n">
         <v>0</v>
@@ -8042,7 +8042,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -8986,7 +8990,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NFG.xlsx
+++ b/output/pdf_financials_xlsx/NFG.xlsx
@@ -1848,19 +1848,19 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>2.5732</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>5.588742</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>5.207323</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>3.082655</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>8.684103</v>
       </c>
     </row>
     <row r="65">
@@ -1923,10 +1923,10 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>1.760131</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>3.651432</v>
       </c>
     </row>
     <row r="68">
@@ -1980,16 +1980,16 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>0.05425</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.081388</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.088958</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>0.053783</v>
       </c>
       <c r="F70" s="3" t="n">
         <v>0</v>
@@ -2002,16 +2002,16 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0</v>
+        <v>0.05425</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>0.081388</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>0.088958</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>0.053783</v>
       </c>
       <c r="F71" s="3" t="n">
         <v>0.503417</v>
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>10.183446</v>
+        <v>10.129196</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>20.144738</v>
+        <v>20.06335</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>12.51528</v>
+        <v>12.426322</v>
       </c>
       <c r="E75" s="3" t="n">
         <v>2.48016</v>
@@ -2199,23 +2199,17 @@
           <t>Debt-to-Equity</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B80" s="3" t="n">
+        <v>0.000442298939931328</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>0.0009750113508533805</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>0.001358074788002141</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>0.001041298871628294</v>
+        <v>0.001849206794490159</v>
       </c>
       <c r="F80" s="3" t="n">
         <v>0.002012831126751236</v>
@@ -5394,7 +5388,11 @@
           <t>Lease liabilities</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -6215,7 +6213,11 @@
           <t>Lease liabilities 8</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E68" s="5" t="n">
         <v>0.05425</v>
       </c>
